--- a/MPOs/off-prem/lytt_pos_displays.xlsx
+++ b/MPOs/off-prem/lytt_pos_displays.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="192">
   <si>
     <t>Values were filtered by:</t>
   </si>
@@ -23,13 +23,13 @@
     <t>Start Date</t>
   </si>
   <si>
-    <t>07/01/2026</t>
+    <t>08/01/2026</t>
   </si>
   <si>
     <t>End Date</t>
   </si>
   <si>
-    <t>08/19/2026</t>
+    <t>08/20/2026</t>
   </si>
   <si>
     <t>Brands</t>
@@ -83,12 +83,45 @@
     <t>Photo</t>
   </si>
   <si>
+    <t>Pablo Lopez</t>
+  </si>
+  <si>
+    <t>Sales Rep</t>
+  </si>
+  <si>
+    <t>Denise Montes</t>
+  </si>
+  <si>
+    <t>26014</t>
+  </si>
+  <si>
+    <t>REGALADO LIQ</t>
+  </si>
+  <si>
+    <t>168 MARKET ST</t>
+  </si>
+  <si>
+    <t>PASSAIC</t>
+  </si>
+  <si>
+    <t>BOSTON BEER COMPANY</t>
+  </si>
+  <si>
+    <t>LYTT</t>
+  </si>
+  <si>
+    <t>LYTT BLUE RASPBERRY</t>
+  </si>
+  <si>
+    <t>24 PK</t>
+  </si>
+  <si>
+    <t>08/19/2026 01:26 PM</t>
+  </si>
+  <si>
     <t>phil Ernst</t>
   </si>
   <si>
-    <t>Sales Rep</t>
-  </si>
-  <si>
     <t>Michael Engel</t>
   </si>
   <si>
@@ -104,18 +137,6 @@
     <t>PARAMUS</t>
   </si>
   <si>
-    <t>BOSTON BEER COMPANY</t>
-  </si>
-  <si>
-    <t>LYTT</t>
-  </si>
-  <si>
-    <t>LYTT BLUE RASPBERRY</t>
-  </si>
-  <si>
-    <t>24 PK</t>
-  </si>
-  <si>
     <t>08/18/2026 03:19 PM</t>
   </si>
   <si>
@@ -123,21 +144,6 @@
   </si>
   <si>
     <t>Sales Associate</t>
-  </si>
-  <si>
-    <t>Denise Montes</t>
-  </si>
-  <si>
-    <t>26014</t>
-  </si>
-  <si>
-    <t>REGALADO LIQ</t>
-  </si>
-  <si>
-    <t>168 MARKET ST</t>
-  </si>
-  <si>
-    <t>PASSAIC</t>
   </si>
   <si>
     <t>08/18/2026 01:41 PM</t>
@@ -981,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O113"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -1086,7 +1092,7 @@
         <v>32</v>
       </c>
       <c r="M2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>33</v>
@@ -1103,22 +1109,22 @@
         <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>29</v>
@@ -1133,10 +1139,10 @@
         <v>32</v>
       </c>
       <c r="M3" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>21</v>
@@ -1147,25 +1153,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>29</v>
@@ -1174,7 +1180,7 @@
         <v>30</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>32</v>
@@ -1183,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>21</v>
@@ -1194,43 +1200,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="2">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>21</v>
@@ -1241,25 +1247,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>29</v>
@@ -1268,7 +1274,7 @@
         <v>30</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>32</v>
@@ -1277,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>21</v>
@@ -1288,25 +1294,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>29</v>
@@ -1315,7 +1321,7 @@
         <v>30</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>32</v>
@@ -1324,7 +1330,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>21</v>
@@ -1335,43 +1341,43 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="2">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>21</v>
@@ -1382,35 +1388,35 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="L9" s="2" t="s">
         <v>32</v>
       </c>
@@ -1418,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>21</v>
@@ -1429,25 +1435,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>29</v>
@@ -1456,7 +1462,7 @@
         <v>30</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>32</v>
@@ -1465,7 +1471,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>21</v>
@@ -1476,25 +1482,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>29</v>
@@ -1503,7 +1509,7 @@
         <v>30</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>32</v>
@@ -1512,7 +1518,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>21</v>
@@ -1523,43 +1529,43 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="2">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12" s="2">
-        <v>24</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>21</v>
@@ -1570,43 +1576,43 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="2">
+        <v>24</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13" s="2">
-        <v>1</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>21</v>
@@ -1617,25 +1623,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>29</v>
@@ -1644,7 +1650,7 @@
         <v>30</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>32</v>
@@ -1653,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>21</v>
@@ -1664,25 +1670,25 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>29</v>
@@ -1691,7 +1697,7 @@
         <v>30</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>32</v>
@@ -1700,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>21</v>
@@ -1711,25 +1717,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>29</v>
@@ -1738,7 +1744,7 @@
         <v>30</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>32</v>
@@ -1747,7 +1753,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>21</v>
@@ -1758,25 +1764,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>29</v>
@@ -1785,16 +1791,16 @@
         <v>30</v>
       </c>
       <c r="K17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="2">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17" s="2">
-        <v>1</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>21</v>
@@ -1805,25 +1811,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>29</v>
@@ -1832,7 +1838,7 @@
         <v>30</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>32</v>
@@ -1841,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>21</v>
@@ -1852,25 +1858,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>29</v>
@@ -1879,7 +1885,7 @@
         <v>30</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>32</v>
@@ -1888,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>21</v>
@@ -1899,35 +1905,35 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="L20" s="2" t="s">
         <v>32</v>
       </c>
@@ -1935,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>21</v>
@@ -1946,35 +1952,35 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="L21" s="2" t="s">
         <v>32</v>
       </c>
@@ -1982,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>21</v>
@@ -1993,25 +1999,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>29</v>
@@ -2020,7 +2026,7 @@
         <v>30</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>32</v>
@@ -2029,7 +2035,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>21</v>
@@ -2040,43 +2046,43 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="I23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="2">
+        <v>1</v>
+      </c>
+      <c r="N23" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M23" s="2">
-        <v>5</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>21</v>
@@ -2087,43 +2093,43 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="M24" s="2">
+        <v>5</v>
+      </c>
+      <c r="N24" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M24" s="2">
-        <v>10</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>21</v>
@@ -2134,25 +2140,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>29</v>
@@ -2161,7 +2167,7 @@
         <v>30</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>32</v>
@@ -2170,7 +2176,7 @@
         <v>10</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O25" s="3" t="s">
         <v>21</v>
@@ -2181,25 +2187,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>29</v>
@@ -2208,7 +2214,7 @@
         <v>30</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>32</v>
@@ -2217,7 +2223,7 @@
         <v>10</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>21</v>
@@ -2228,25 +2234,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>29</v>
@@ -2255,7 +2261,7 @@
         <v>30</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>32</v>
@@ -2264,7 +2270,7 @@
         <v>10</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>21</v>
@@ -2275,25 +2281,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>29</v>
@@ -2302,16 +2308,16 @@
         <v>30</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M28" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>21</v>
@@ -2322,43 +2328,43 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="I29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="2">
+        <v>3</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M29" s="2">
-        <v>2</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>21</v>
@@ -2369,25 +2375,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>29</v>
@@ -2396,16 +2402,16 @@
         <v>30</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M30" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>21</v>
@@ -2416,25 +2422,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>29</v>
@@ -2443,16 +2449,16 @@
         <v>30</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M31" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O31" s="3" t="s">
         <v>21</v>
@@ -2463,43 +2469,43 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M32" s="2">
+        <v>1</v>
+      </c>
+      <c r="N32" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M32" s="2">
-        <v>1</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>21</v>
@@ -2510,25 +2516,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>29</v>
@@ -2537,7 +2543,7 @@
         <v>30</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>32</v>
@@ -2546,7 +2552,7 @@
         <v>1</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>21</v>
@@ -2557,25 +2563,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>29</v>
@@ -2584,7 +2590,7 @@
         <v>30</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>32</v>
@@ -2593,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>21</v>
@@ -2604,25 +2610,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>29</v>
@@ -2631,7 +2637,7 @@
         <v>30</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>32</v>
@@ -2640,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>21</v>
@@ -2651,25 +2657,25 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>29</v>
@@ -2678,7 +2684,7 @@
         <v>30</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>32</v>
@@ -2687,7 +2693,7 @@
         <v>1</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O36" s="3" t="s">
         <v>21</v>
@@ -2698,25 +2704,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>29</v>
@@ -2725,7 +2731,7 @@
         <v>30</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>32</v>
@@ -2734,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O37" s="3" t="s">
         <v>21</v>
@@ -2745,7 +2751,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>23</v>
@@ -2754,16 +2760,16 @@
         <v>24</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>29</v>
@@ -2772,16 +2778,16 @@
         <v>30</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M38" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O38" s="3" t="s">
         <v>21</v>
@@ -2792,25 +2798,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>29</v>
@@ -2819,16 +2825,16 @@
         <v>30</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M39" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>21</v>
@@ -2839,25 +2845,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>29</v>
@@ -2866,16 +2872,16 @@
         <v>30</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M40" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O40" s="3" t="s">
         <v>21</v>
@@ -2886,25 +2892,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>29</v>
@@ -2913,16 +2919,16 @@
         <v>30</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>21</v>
@@ -2933,43 +2939,43 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" s="2">
+        <v>2</v>
+      </c>
+      <c r="N42" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M42" s="2">
-        <v>1</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>21</v>
@@ -2980,25 +2986,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>29</v>
@@ -3007,7 +3013,7 @@
         <v>30</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>32</v>
@@ -3016,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>21</v>
@@ -3027,25 +3033,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>29</v>
@@ -3054,7 +3060,7 @@
         <v>30</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>32</v>
@@ -3063,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>21</v>
@@ -3074,25 +3080,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>29</v>
@@ -3101,7 +3107,7 @@
         <v>30</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>32</v>
@@ -3110,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>21</v>
@@ -3121,25 +3127,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>29</v>
@@ -3148,7 +3154,7 @@
         <v>30</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>32</v>
@@ -3157,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>21</v>
@@ -3168,25 +3174,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>29</v>
@@ -3195,7 +3201,7 @@
         <v>30</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>32</v>
@@ -3204,7 +3210,7 @@
         <v>1</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>21</v>
@@ -3215,43 +3221,43 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="2" t="s">
+      <c r="I48" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M48" s="2">
+        <v>1</v>
+      </c>
+      <c r="N48" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M48" s="2">
-        <v>1</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>21</v>
@@ -3262,25 +3268,25 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>29</v>
@@ -3289,7 +3295,7 @@
         <v>30</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>32</v>
@@ -3298,7 +3304,7 @@
         <v>1</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>21</v>
@@ -3309,25 +3315,25 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>29</v>
@@ -3336,7 +3342,7 @@
         <v>30</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>32</v>
@@ -3345,7 +3351,7 @@
         <v>1</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>21</v>
@@ -3356,25 +3362,25 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>29</v>
@@ -3383,7 +3389,7 @@
         <v>30</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>32</v>
@@ -3392,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O51" s="3" t="s">
         <v>21</v>
@@ -3403,25 +3409,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>29</v>
@@ -3430,7 +3436,7 @@
         <v>30</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>32</v>
@@ -3439,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>21</v>
@@ -3450,25 +3456,25 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>29</v>
@@ -3477,7 +3483,7 @@
         <v>30</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>32</v>
@@ -3486,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O53" s="3" t="s">
         <v>21</v>
@@ -3497,43 +3503,43 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="I54" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M54" s="2">
+        <v>1</v>
+      </c>
+      <c r="N54" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M54" s="2">
-        <v>1</v>
-      </c>
-      <c r="N54" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>21</v>
@@ -3544,25 +3550,25 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>29</v>
@@ -3571,7 +3577,7 @@
         <v>30</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>32</v>
@@ -3580,7 +3586,7 @@
         <v>1</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O55" s="3" t="s">
         <v>21</v>
@@ -3591,25 +3597,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>29</v>
@@ -3618,7 +3624,7 @@
         <v>30</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>32</v>
@@ -3627,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>21</v>
@@ -3638,25 +3644,25 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>29</v>
@@ -3665,7 +3671,7 @@
         <v>30</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>32</v>
@@ -3674,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>21</v>
@@ -3685,25 +3691,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>29</v>
@@ -3712,7 +3718,7 @@
         <v>30</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>32</v>
@@ -3721,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>21</v>
@@ -3732,25 +3738,25 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>29</v>
@@ -3759,7 +3765,7 @@
         <v>30</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>32</v>
@@ -3768,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>21</v>
@@ -3779,43 +3785,43 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H60" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E60" s="2" t="s">
+      <c r="I60" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M60" s="2">
+        <v>1</v>
+      </c>
+      <c r="N60" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M60" s="2">
-        <v>1</v>
-      </c>
-      <c r="N60" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>21</v>
@@ -3826,25 +3832,25 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>29</v>
@@ -3853,7 +3859,7 @@
         <v>30</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>32</v>
@@ -3862,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O61" s="3" t="s">
         <v>21</v>
@@ -3873,25 +3879,25 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>29</v>
@@ -3900,7 +3906,7 @@
         <v>30</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>32</v>
@@ -3909,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>21</v>
@@ -3920,25 +3926,25 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>29</v>
@@ -3947,7 +3953,7 @@
         <v>30</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>32</v>
@@ -3956,7 +3962,7 @@
         <v>1</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O63" s="3" t="s">
         <v>21</v>
@@ -3967,25 +3973,25 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>29</v>
@@ -3994,7 +4000,7 @@
         <v>30</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>32</v>
@@ -4003,7 +4009,7 @@
         <v>1</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O64" s="3" t="s">
         <v>21</v>
@@ -4014,25 +4020,25 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>29</v>
@@ -4041,7 +4047,7 @@
         <v>30</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>32</v>
@@ -4050,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O65" s="3" t="s">
         <v>21</v>
@@ -4061,43 +4067,43 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M66" s="2">
+        <v>1</v>
+      </c>
+      <c r="N66" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M66" s="2">
-        <v>1</v>
-      </c>
-      <c r="N66" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>21</v>
@@ -4108,25 +4114,25 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E67" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>29</v>
@@ -4135,7 +4141,7 @@
         <v>30</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>32</v>
@@ -4144,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>21</v>
@@ -4155,25 +4161,25 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E68" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>29</v>
@@ -4182,7 +4188,7 @@
         <v>30</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>32</v>
@@ -4191,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>21</v>
@@ -4202,25 +4208,25 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E69" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>29</v>
@@ -4229,7 +4235,7 @@
         <v>30</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>32</v>
@@ -4238,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O69" s="3" t="s">
         <v>21</v>
@@ -4249,25 +4255,25 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E70" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>29</v>
@@ -4276,7 +4282,7 @@
         <v>30</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>32</v>
@@ -4285,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>21</v>
@@ -4296,25 +4302,25 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E71" s="2" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>29</v>
@@ -4323,7 +4329,7 @@
         <v>30</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>32</v>
@@ -4332,7 +4338,7 @@
         <v>1</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O71" s="3" t="s">
         <v>21</v>
@@ -4343,25 +4349,25 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E72" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>29</v>
@@ -4370,7 +4376,7 @@
         <v>30</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>32</v>
@@ -4379,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>21</v>
@@ -4390,25 +4396,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C73" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E73" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>29</v>
@@ -4417,7 +4423,7 @@
         <v>30</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>32</v>
@@ -4426,7 +4432,7 @@
         <v>1</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>21</v>
@@ -4437,25 +4443,25 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E74" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>29</v>
@@ -4464,7 +4470,7 @@
         <v>30</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>32</v>
@@ -4473,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O74" s="3" t="s">
         <v>21</v>
@@ -4484,25 +4490,25 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E75" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>29</v>
@@ -4511,7 +4517,7 @@
         <v>30</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>32</v>
@@ -4520,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O75" s="3" t="s">
         <v>21</v>
@@ -4531,43 +4537,43 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E76" s="2" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="F76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M76" s="2">
+        <v>1</v>
+      </c>
+      <c r="N76" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M76" s="2">
-        <v>1</v>
-      </c>
-      <c r="N76" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>21</v>
@@ -4578,25 +4584,25 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E77" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>29</v>
@@ -4605,7 +4611,7 @@
         <v>30</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>32</v>
@@ -4614,7 +4620,7 @@
         <v>1</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O77" s="3" t="s">
         <v>21</v>
@@ -4625,25 +4631,25 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E78" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>29</v>
@@ -4652,7 +4658,7 @@
         <v>30</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>32</v>
@@ -4661,7 +4667,7 @@
         <v>1</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>21</v>
@@ -4672,25 +4678,25 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E79" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>29</v>
@@ -4699,7 +4705,7 @@
         <v>30</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>32</v>
@@ -4708,7 +4714,7 @@
         <v>1</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O79" s="3" t="s">
         <v>21</v>
@@ -4719,43 +4725,43 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E80" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="I80" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M80" s="2">
+        <v>1</v>
+      </c>
+      <c r="N80" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M80" s="2">
-        <v>12</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="O80" s="3" t="s">
         <v>21</v>
@@ -4766,43 +4772,43 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E81" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="H81" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M81" s="2">
+        <v>12</v>
+      </c>
+      <c r="N81" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J81" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M81" s="2">
-        <v>1</v>
-      </c>
-      <c r="N81" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>21</v>
@@ -4813,25 +4819,25 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C82" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E82" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>29</v>
@@ -4840,7 +4846,7 @@
         <v>30</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>32</v>
@@ -4849,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O82" s="3" t="s">
         <v>21</v>
@@ -4860,25 +4866,25 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C83" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="E83" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>29</v>
@@ -4887,7 +4893,7 @@
         <v>30</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>32</v>
@@ -4896,7 +4902,7 @@
         <v>1</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>21</v>
@@ -4907,43 +4913,43 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E84" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H84" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="I84" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M84" s="2">
+        <v>1</v>
+      </c>
+      <c r="N84" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M84" s="2">
-        <v>1</v>
-      </c>
-      <c r="N84" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="O84" s="3" t="s">
         <v>21</v>
@@ -4954,25 +4960,25 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>29</v>
@@ -4981,7 +4987,7 @@
         <v>30</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>32</v>
@@ -4990,7 +4996,7 @@
         <v>1</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O85" s="3" t="s">
         <v>21</v>
@@ -5001,25 +5007,25 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>29</v>
@@ -5028,7 +5034,7 @@
         <v>30</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>32</v>
@@ -5037,7 +5043,7 @@
         <v>1</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O86" s="3" t="s">
         <v>21</v>
@@ -5048,25 +5054,25 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>29</v>
@@ -5075,7 +5081,7 @@
         <v>30</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>32</v>
@@ -5084,7 +5090,7 @@
         <v>1</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O87" s="3" t="s">
         <v>21</v>
@@ -5095,25 +5101,25 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>29</v>
@@ -5122,7 +5128,7 @@
         <v>30</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>32</v>
@@ -5131,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O88" s="3" t="s">
         <v>21</v>
@@ -5142,25 +5148,25 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>29</v>
@@ -5169,7 +5175,7 @@
         <v>30</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>32</v>
@@ -5178,7 +5184,7 @@
         <v>1</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>21</v>
@@ -5189,43 +5195,43 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E90" s="2" t="s">
+      <c r="I90" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M90" s="2">
+        <v>1</v>
+      </c>
+      <c r="N90" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J90" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M90" s="2">
-        <v>1</v>
-      </c>
-      <c r="N90" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="O90" s="3" t="s">
         <v>21</v>
@@ -5236,25 +5242,25 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>29</v>
@@ -5263,7 +5269,7 @@
         <v>30</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>32</v>
@@ -5272,7 +5278,7 @@
         <v>1</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>21</v>
@@ -5283,25 +5289,25 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>29</v>
@@ -5310,7 +5316,7 @@
         <v>30</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>32</v>
@@ -5319,7 +5325,7 @@
         <v>1</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O92" s="3" t="s">
         <v>21</v>
@@ -5330,25 +5336,25 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>29</v>
@@ -5357,7 +5363,7 @@
         <v>30</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>32</v>
@@ -5366,7 +5372,7 @@
         <v>1</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O93" s="3" t="s">
         <v>21</v>
@@ -5377,25 +5383,25 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>29</v>
@@ -5404,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>32</v>
@@ -5413,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>21</v>
@@ -5424,25 +5430,25 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>29</v>
@@ -5451,7 +5457,7 @@
         <v>30</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>32</v>
@@ -5460,7 +5466,7 @@
         <v>1</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O95" s="3" t="s">
         <v>21</v>
@@ -5471,43 +5477,43 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="E96" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="I96" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M96" s="2">
+        <v>1</v>
+      </c>
+      <c r="N96" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J96" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M96" s="2">
-        <v>1</v>
-      </c>
-      <c r="N96" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>21</v>
@@ -5518,25 +5524,25 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>29</v>
@@ -5545,7 +5551,7 @@
         <v>30</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>32</v>
@@ -5554,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O97" s="3" t="s">
         <v>21</v>
@@ -5565,25 +5571,25 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>29</v>
@@ -5592,7 +5598,7 @@
         <v>30</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>32</v>
@@ -5601,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O98" s="3" t="s">
         <v>21</v>
@@ -5612,25 +5618,25 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>29</v>
@@ -5639,7 +5645,7 @@
         <v>30</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>32</v>
@@ -5648,7 +5654,7 @@
         <v>1</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O99" s="3" t="s">
         <v>21</v>
@@ -5659,25 +5665,25 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>29</v>
@@ -5686,7 +5692,7 @@
         <v>30</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>32</v>
@@ -5695,7 +5701,7 @@
         <v>1</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>21</v>
@@ -5706,25 +5712,25 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>29</v>
@@ -5733,7 +5739,7 @@
         <v>30</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>32</v>
@@ -5742,7 +5748,7 @@
         <v>1</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>21</v>
@@ -5753,43 +5759,43 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E102" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="H102" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M102" s="2">
+        <v>1</v>
+      </c>
+      <c r="N102" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L102" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M102" s="2">
-        <v>12</v>
-      </c>
-      <c r="N102" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>21</v>
@@ -5800,43 +5806,43 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>154</v>
+        <v>57</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E103" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="H103" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M103" s="2">
+        <v>12</v>
+      </c>
+      <c r="N103" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M103" s="2">
-        <v>1</v>
-      </c>
-      <c r="N103" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="O103" s="3" t="s">
         <v>21</v>
@@ -5847,25 +5853,25 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>29</v>
@@ -5874,7 +5880,7 @@
         <v>30</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>32</v>
@@ -5883,7 +5889,7 @@
         <v>1</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O104" s="3" t="s">
         <v>21</v>
@@ -5894,25 +5900,25 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>29</v>
@@ -5921,7 +5927,7 @@
         <v>30</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>32</v>
@@ -5930,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O105" s="3" t="s">
         <v>21</v>
@@ -5941,25 +5947,25 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I106" s="2" t="s">
         <v>29</v>
@@ -5968,7 +5974,7 @@
         <v>30</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>32</v>
@@ -5977,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O106" s="3" t="s">
         <v>21</v>
@@ -5988,25 +5994,25 @@
         <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>29</v>
@@ -6015,7 +6021,7 @@
         <v>30</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>32</v>
@@ -6024,7 +6030,7 @@
         <v>1</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O107" s="3" t="s">
         <v>21</v>
@@ -6035,25 +6041,25 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>29</v>
@@ -6062,7 +6068,7 @@
         <v>30</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>32</v>
@@ -6071,7 +6077,7 @@
         <v>1</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O108" s="3" t="s">
         <v>21</v>
@@ -6082,43 +6088,43 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="E109" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F109" s="2" t="s">
+      <c r="I109" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M109" s="2">
+        <v>1</v>
+      </c>
+      <c r="N109" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K109" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L109" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M109" s="2">
-        <v>12</v>
-      </c>
-      <c r="N109" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="O109" s="3" t="s">
         <v>21</v>
@@ -6129,25 +6135,25 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E110" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F110" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="H110" s="2" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>29</v>
@@ -6156,7 +6162,7 @@
         <v>30</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>32</v>
@@ -6165,7 +6171,7 @@
         <v>12</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O110" s="3" t="s">
         <v>21</v>
@@ -6176,25 +6182,25 @@
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E111" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="H111" s="2" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="I111" s="2" t="s">
         <v>29</v>
@@ -6203,7 +6209,7 @@
         <v>30</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>32</v>
@@ -6212,7 +6218,7 @@
         <v>12</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="O111" s="3" t="s">
         <v>21</v>
@@ -6223,43 +6229,43 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E112" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F112" s="2" t="s">
+      <c r="H112" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M112" s="2">
+        <v>12</v>
+      </c>
+      <c r="N112" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J112" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K112" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L112" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M112" s="2">
-        <v>30</v>
-      </c>
-      <c r="N112" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="O112" s="3" t="s">
         <v>21</v>
@@ -6270,45 +6276,92 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G113" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M113" s="2">
+        <v>30</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="O113" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" s="2">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="H113" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K113" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L113" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M113" s="2">
-        <v>30</v>
-      </c>
-      <c r="N113" s="2" t="s">
+      <c r="F114" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G114" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="O113" s="3" t="s">
+      <c r="H114" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M114" s="2">
+        <v>30</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="O114" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6426,6 +6479,7 @@
     <hyperlink ref="O111" r:id="rId110"/>
     <hyperlink ref="O112" r:id="rId111"/>
     <hyperlink ref="O113" r:id="rId112"/>
+    <hyperlink ref="O114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MPOs/off-prem/lytt_pos_displays.xlsx
+++ b/MPOs/off-prem/lytt_pos_displays.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -597,22 +597,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 01:19 PM</t>
+          <t>08/21/2026 12:25 PM</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 01:19 PM</t>
+          <t>08/21/2026 12:25 PM</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -743,22 +743,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 01:19 PM</t>
+          <t>08/21/2026 12:25 PM</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -816,22 +816,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 01:19 PM</t>
+          <t>08/21/2026 12:25 PM</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -889,22 +889,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 01:19 PM</t>
+          <t>08/21/2026 12:25 PM</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -962,22 +962,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 01:19 PM</t>
+          <t>08/21/2026 12:25 PM</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1035,22 +1035,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 12:51 PM</t>
+          <t>08/21/2026 12:03 PM</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 12:51 PM</t>
+          <t>08/21/2026 12:03 PM</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 12:51 PM</t>
+          <t>08/21/2026 12:03 PM</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -1254,22 +1254,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 12:51 PM</t>
+          <t>08/21/2026 12:03 PM</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1327,22 +1327,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 12:51 PM</t>
+          <t>08/21/2026 12:03 PM</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1400,22 +1400,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 12:51 PM</t>
+          <t>08/21/2026 12:03 PM</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Javier Melo</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>EAST SIDE BAR LIQUORS</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>442 10TH AVE</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1512,11 +1512,11 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>08/19/2026 01:26 PM</t>
+          <t>08/21/2026 11:26 AM</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1541,27 +1541,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>SHOP RITE OF WALLINGTON</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>375 PATERSON AVE</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1585,11 +1585,11 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 03:19 PM</t>
+          <t>08/21/2026 11:20 AM</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1619,22 +1619,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>SHOP RITE OF WALLINGTON</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>375 PATERSON AVE</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:41 PM</t>
+          <t>08/21/2026 11:20 AM</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1692,22 +1692,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>SHOP RITE OF WALLINGTON</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>375 PATERSON AVE</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:41 PM</t>
+          <t>08/21/2026 11:20 AM</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1765,22 +1765,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>SHOP RITE OF WALLINGTON</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>375 PATERSON AVE</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:05 PM</t>
+          <t>08/21/2026 11:20 AM</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1838,22 +1838,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>SHOP RITE OF WALLINGTON</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>375 PATERSON AVE</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:05 PM</t>
+          <t>08/21/2026 11:20 AM</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1911,22 +1911,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>SHOP RITE OF WALLINGTON</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>375 PATERSON AVE</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:05 PM</t>
+          <t>08/21/2026 11:20 AM</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:05 PM</t>
+          <t>08/20/2026 01:19 PM</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 12:32 PM</t>
+          <t>08/20/2026 01:19 PM</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 12:32 PM</t>
+          <t>08/20/2026 01:19 PM</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 12:32 PM</t>
+          <t>08/20/2026 01:19 PM</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2276,22 +2276,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>C TOWN SUPERMARKET(P)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>444 20TH AVENUE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:24 AM</t>
+          <t>08/20/2026 01:19 PM</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2349,22 +2349,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>WORLD OF WINE &amp; LIQUOR</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>419 VALLEY BROOK AVE.</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:04 AM</t>
+          <t>08/20/2026 01:19 PM</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2422,22 +2422,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>WORLD OF WINE &amp; LIQUOR</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>419 VALLEY BROOK AVE.</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:04 AM</t>
+          <t>08/20/2026 12:51 PM</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2495,22 +2495,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>WORLD OF WINE &amp; LIQUOR</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>419 VALLEY BROOK AVE.</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:04 AM</t>
+          <t>08/20/2026 12:51 PM</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>WORLD OF WINE &amp; LIQUOR</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>419 VALLEY BROOK AVE.</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:04 AM</t>
+          <t>08/20/2026 12:51 PM</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2641,22 +2641,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>WORLD OF WINE &amp; LIQUOR</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>419 VALLEY BROOK AVE.</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:04 AM</t>
+          <t>08/20/2026 12:51 PM</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2714,22 +2714,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>WORLD OF WINE &amp; LIQUOR</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>419 VALLEY BROOK AVE.</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:04 AM</t>
+          <t>08/20/2026 12:51 PM</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2787,22 +2787,22 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>CAPRI DELI&amp;LIQ (P)</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>226 PATERSON AVE</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 10:30 AM</t>
+          <t>08/20/2026 12:51 PM</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2860,22 +2860,22 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>CAPRI DELI&amp;LIQ (P)</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>226 PATERSON AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2899,11 +2899,11 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 10:30 AM</t>
+          <t>08/19/2026 01:26 PM</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -2918,37 +2918,37 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>CAPRI DELI&amp;LIQ (P)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>226 PATERSON AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2972,11 +2972,11 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 10:30 AM</t>
+          <t>08/18/2026 03:19 PM</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -3006,22 +3006,22 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>CAPRI DELI&amp;LIQ (P)</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>226 PATERSON AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 10:30 AM</t>
+          <t>08/18/2026 01:41 PM</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Jay Tabasco</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3074,27 +3074,27 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>190304</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>SHOPPERS DISC LIQUOR</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>65-69 N BEVERWYCK RD</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>LAKE HIAWATHA</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -3109,20 +3109,20 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12 PK BTL</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 09:41 AM</t>
+          <t>08/18/2026 01:41 PM</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -3137,37 +3137,37 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -3191,11 +3191,11 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 01:26 PM</t>
+          <t>08/18/2026 01:05 PM</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -3210,37 +3210,37 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3264,11 +3264,11 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 01:26 PM</t>
+          <t>08/18/2026 01:05 PM</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -3283,37 +3283,37 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 01:26 PM</t>
+          <t>08/18/2026 01:05 PM</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -3356,37 +3356,37 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3410,11 +3410,11 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 01:26 PM</t>
+          <t>08/18/2026 01:05 PM</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -3429,37 +3429,37 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3483,11 +3483,11 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 01:26 PM</t>
+          <t>08/18/2026 12:32 PM</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -3502,37 +3502,37 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3556,11 +3556,11 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 12:11 PM</t>
+          <t>08/18/2026 12:32 PM</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -3575,37 +3575,37 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3629,11 +3629,11 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 12:11 PM</t>
+          <t>08/18/2026 12:32 PM</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Javier Melo</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3658,27 +3658,27 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>C TOWN SUPERMARKET(P)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>444 20TH AVENUE</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -3702,11 +3702,11 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:23 AM</t>
+          <t>08/18/2026 11:24 AM</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -3736,22 +3736,22 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW LIQUOR (P)</t>
+          <t>WORLD OF WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>292 LAKEVIEW AVE</t>
+          <t>419 VALLEY BROOK AVE.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:00 AM</t>
+          <t>08/18/2026 11:04 AM</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -3809,22 +3809,22 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW LIQUOR (P)</t>
+          <t>WORLD OF WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>292 LAKEVIEW AVE</t>
+          <t>419 VALLEY BROOK AVE.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:00 AM</t>
+          <t>08/18/2026 11:04 AM</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -3882,22 +3882,22 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW LIQUOR (P)</t>
+          <t>WORLD OF WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>292 LAKEVIEW AVE</t>
+          <t>419 VALLEY BROOK AVE.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:00 AM</t>
+          <t>08/18/2026 11:04 AM</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
@@ -3955,22 +3955,22 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW LIQUOR (P)</t>
+          <t>WORLD OF WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>292 LAKEVIEW AVE</t>
+          <t>419 VALLEY BROOK AVE.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:00 AM</t>
+          <t>08/18/2026 11:04 AM</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW LIQUOR (P)</t>
+          <t>WORLD OF WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>292 LAKEVIEW AVE</t>
+          <t>419 VALLEY BROOK AVE.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:00 AM</t>
+          <t>08/18/2026 11:04 AM</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
@@ -4101,22 +4101,22 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW LIQUOR (P)</t>
+          <t>WORLD OF WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>292 LAKEVIEW AVE</t>
+          <t>419 VALLEY BROOK AVE.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:00 AM</t>
+          <t>08/18/2026 11:04 AM</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -4159,37 +4159,37 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -4213,11 +4213,11 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>08/14/2026 12:06 PM</t>
+          <t>08/18/2026 10:30 AM</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
@@ -4232,37 +4232,37 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4286,11 +4286,11 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>08/14/2026 11:41 AM</t>
+          <t>08/18/2026 10:30 AM</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -4305,37 +4305,37 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>08/14/2026 11:39 AM</t>
+          <t>08/18/2026 10:30 AM</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
@@ -4378,37 +4378,37 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -4432,11 +4432,11 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>08/14/2026 11:38 AM</t>
+          <t>08/18/2026 10:30 AM</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Gallagher</t>
+          <t>Jay Tabasco</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4461,27 +4461,27 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Christopher McCrohan</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>190304</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>BEST CELLARS (WANAQUE)</t>
+          <t>SHOPPERS DISC LIQUOR</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1069 RINGWOOD AVE</t>
+          <t>65-69 N BEVERWYCK RD</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>WANAQUE</t>
+          <t>LAKE HIAWATHA</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -4501,15 +4501,15 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>12 PK BTL</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:38 PM</t>
+          <t>08/18/2026 09:41 AM</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -4524,37 +4524,37 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Gallagher</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Christopher McCrohan</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>BEST CELLARS (WANAQUE)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1069 RINGWOOD AVE</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>WANAQUE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -4578,11 +4578,11 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:38 PM</t>
+          <t>08/17/2026 01:26 PM</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -4597,37 +4597,37 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Gallagher</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Christopher McCrohan</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>BEST CELLARS (WANAQUE)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1069 RINGWOOD AVE</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>WANAQUE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -4651,11 +4651,11 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:38 PM</t>
+          <t>08/17/2026 01:26 PM</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
@@ -4670,37 +4670,37 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Gallagher</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Christopher McCrohan</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>BEST CELLARS (WANAQUE)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1069 RINGWOOD AVE</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>WANAQUE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -4724,11 +4724,11 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:38 PM</t>
+          <t>08/17/2026 01:26 PM</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -4743,37 +4743,37 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Gallagher</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Christopher McCrohan</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>BEST CELLARS (WANAQUE)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1069 RINGWOOD AVE</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>WANAQUE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -4797,11 +4797,11 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:38 PM</t>
+          <t>08/17/2026 01:26 PM</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
@@ -4816,37 +4816,37 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Gallagher</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Christopher McCrohan</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>BEST CELLARS (WANAQUE)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1069 RINGWOOD AVE</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>WANAQUE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -4870,11 +4870,11 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:38 PM</t>
+          <t>08/17/2026 01:26 PM</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4904,22 +4904,22 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4943,11 +4943,11 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:02 PM</t>
+          <t>08/17/2026 12:11 PM</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4977,22 +4977,22 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -5016,11 +5016,11 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:02 PM</t>
+          <t>08/17/2026 12:11 PM</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5050,22 +5050,22 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:02 PM</t>
+          <t>08/17/2026 10:23 AM</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5118,27 +5118,27 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>RAINBOW LIQUOR (P)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>292 LAKEVIEW AVE</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:02 PM</t>
+          <t>08/17/2026 10:00 AM</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5191,27 +5191,27 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>RAINBOW LIQUOR (P)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>292 LAKEVIEW AVE</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:02 PM</t>
+          <t>08/17/2026 10:00 AM</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5264,27 +5264,27 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>RAINBOW LIQUOR (P)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>292 LAKEVIEW AVE</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:02 PM</t>
+          <t>08/17/2026 10:00 AM</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5337,27 +5337,27 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>LINWOOD WINE-LINWOOD PLAZA</t>
+          <t>RAINBOW LIQUOR (P)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>102 LINWOOD PLAZA</t>
+          <t>292 LAKEVIEW AVE</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>FORT LEE</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 11:05 AM</t>
+          <t>08/17/2026 10:00 AM</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5410,27 +5410,27 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>LINWOOD WINE-LINWOOD PLAZA</t>
+          <t>RAINBOW LIQUOR (P)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>102 LINWOOD PLAZA</t>
+          <t>292 LAKEVIEW AVE</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>FORT LEE</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 11:05 AM</t>
+          <t>08/17/2026 10:00 AM</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5483,27 +5483,27 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>LINWOOD WINE-LINWOOD PLAZA</t>
+          <t>RAINBOW LIQUOR (P)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>102 LINWOOD PLAZA</t>
+          <t>292 LAKEVIEW AVE</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>FORT LEE</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 11:05 AM</t>
+          <t>08/17/2026 10:00 AM</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5561,22 +5561,22 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>LINWOOD WINE-LINWOOD PLAZA</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>102 LINWOOD PLAZA</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>FORT LEE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -5600,11 +5600,11 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 11:05 AM</t>
+          <t>08/14/2026 12:06 PM</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5634,22 +5634,22 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>LINWOOD WINE-LINWOOD PLAZA</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>102 LINWOOD PLAZA</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>FORT LEE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -5673,11 +5673,11 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 11:05 AM</t>
+          <t>08/14/2026 11:41 AM</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5707,22 +5707,22 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>LINWOOD WINE-LINWOOD PLAZA</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>102 LINWOOD PLAZA</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>FORT LEE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 11:05 AM</t>
+          <t>08/14/2026 11:39 AM</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5775,27 +5775,27 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -5819,11 +5819,11 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 10:51 AM</t>
+          <t>08/14/2026 11:38 AM</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
@@ -5838,37 +5838,37 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Vaughn Gallagher</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Christopher McCrohan</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>BEST CELLARS (WANAQUE)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>1069 RINGWOOD AVE</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WANAQUE</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 10:51 AM</t>
+          <t>08/13/2026 01:38 PM</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
@@ -5911,37 +5911,37 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Vaughn Gallagher</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Christopher McCrohan</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>BEST CELLARS (WANAQUE)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>1069 RINGWOOD AVE</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WANAQUE</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 10:51 AM</t>
+          <t>08/13/2026 01:38 PM</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
@@ -5984,37 +5984,37 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Vaughn Gallagher</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Christopher McCrohan</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>BEST CELLARS (WANAQUE)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>1069 RINGWOOD AVE</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WANAQUE</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 10:51 AM</t>
+          <t>08/13/2026 01:38 PM</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
@@ -6057,37 +6057,37 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Vaughn Gallagher</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Christopher McCrohan</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>BEST CELLARS (WANAQUE)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>1069 RINGWOOD AVE</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WANAQUE</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 10:51 AM</t>
+          <t>08/13/2026 01:38 PM</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
@@ -6130,37 +6130,37 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Vaughn Gallagher</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Christopher McCrohan</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>BEST CELLARS (WANAQUE)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>1069 RINGWOOD AVE</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>WANAQUE</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 10:51 AM</t>
+          <t>08/13/2026 01:38 PM</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Vaughn Gallagher</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6213,27 +6213,27 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Christopher McCrohan</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>BEST CELLARS (WANAQUE)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>1069 RINGWOOD AVE</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>WANAQUE</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 04:00 PM</t>
+          <t>08/13/2026 01:38 PM</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -6291,22 +6291,22 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 04:00 PM</t>
+          <t>08/13/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -6364,22 +6364,22 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 04:00 PM</t>
+          <t>08/13/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -6437,22 +6437,22 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 04:00 PM</t>
+          <t>08/13/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -6510,22 +6510,22 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 04:00 PM</t>
+          <t>08/13/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -6583,22 +6583,22 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:37 PM</t>
+          <t>08/13/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -6656,22 +6656,22 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:37 PM</t>
+          <t>08/13/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -6729,22 +6729,22 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>49027</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>LINWOOD WINE-LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>102 LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>FORT LEE</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:37 PM</t>
+          <t>08/13/2026 11:05 AM</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
@@ -6787,12 +6787,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -6802,22 +6802,22 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>49027</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>LINWOOD WINE-LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>102 LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>FORT LEE</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:37 PM</t>
+          <t>08/13/2026 11:05 AM</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>49027</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>LINWOOD WINE-LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>102 LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>FORT LEE</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:37 PM</t>
+          <t>08/13/2026 11:05 AM</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -6948,22 +6948,22 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>49027</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>THE BOTTLE SHOP</t>
+          <t>LINWOOD WINE-LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>366 ESSEX ST</t>
+          <t>102 LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>FORT LEE</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:14 PM</t>
+          <t>08/13/2026 11:05 AM</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -7021,22 +7021,22 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>49027</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>THE BOTTLE SHOP</t>
+          <t>LINWOOD WINE-LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>366 ESSEX ST</t>
+          <t>102 LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>FORT LEE</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:14 PM</t>
+          <t>08/13/2026 11:05 AM</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -7094,22 +7094,22 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>49027</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>THE BOTTLE SHOP</t>
+          <t>LINWOOD WINE-LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>366 ESSEX ST</t>
+          <t>102 LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>FORT LEE</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:14 PM</t>
+          <t>08/13/2026 11:05 AM</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
@@ -7152,37 +7152,37 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>THE BOTTLE SHOP</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>366 ESSEX ST</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:14 PM</t>
+          <t>08/13/2026 10:51 AM</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7240,22 +7240,22 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>27002</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>PRESIDENT LIQRS (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>158 PRESIDENT ST</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -7279,11 +7279,11 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 02:54 PM</t>
+          <t>08/13/2026 10:51 AM</t>
         </is>
       </c>
       <c r="O93" s="3" t="inlineStr">
@@ -7298,37 +7298,37 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>WIDES DELI &amp; LIQUOR</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>81-85 CENTRAL AVE</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 02:30 PM</t>
+          <t>08/13/2026 10:51 AM</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -7371,37 +7371,37 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>WIDES DELI &amp; LIQUOR</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>81-85 CENTRAL AVE</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 02:30 PM</t>
+          <t>08/13/2026 10:51 AM</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
@@ -7444,37 +7444,37 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>WIDES DELI &amp; LIQUOR</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>81-85 CENTRAL AVE</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 02:30 PM</t>
+          <t>08/13/2026 10:51 AM</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7532,22 +7532,22 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 01:00 PM</t>
+          <t>08/13/2026 10:51 AM</t>
         </is>
       </c>
       <c r="O97" s="3" t="inlineStr">
@@ -7590,37 +7590,37 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 01:00 PM</t>
+          <t>08/11/2026 04:00 PM</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
@@ -7663,37 +7663,37 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 01:00 PM</t>
+          <t>08/11/2026 04:00 PM</t>
         </is>
       </c>
       <c r="O99" s="3" t="inlineStr">
@@ -7736,37 +7736,37 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 01:00 PM</t>
+          <t>08/11/2026 04:00 PM</t>
         </is>
       </c>
       <c r="O100" s="3" t="inlineStr">
@@ -7809,37 +7809,37 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 01:00 PM</t>
+          <t>08/11/2026 04:00 PM</t>
         </is>
       </c>
       <c r="O101" s="3" t="inlineStr">
@@ -7882,37 +7882,37 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 01:00 PM</t>
+          <t>08/11/2026 04:00 PM</t>
         </is>
       </c>
       <c r="O102" s="3" t="inlineStr">
@@ -7955,37 +7955,37 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>231215</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>530 CO RD 515</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>VERNON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:59 AM</t>
+          <t>08/11/2026 03:37 PM</t>
         </is>
       </c>
       <c r="O103" s="3" t="inlineStr">
@@ -8028,37 +8028,37 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>231215</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>530 CO RD 515</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>VERNON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:59 AM</t>
+          <t>08/11/2026 03:37 PM</t>
         </is>
       </c>
       <c r="O104" s="3" t="inlineStr">
@@ -8101,37 +8101,37 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>231215</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>530 CO RD 515</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>VERNON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:59 AM</t>
+          <t>08/11/2026 03:37 PM</t>
         </is>
       </c>
       <c r="O105" s="3" t="inlineStr">
@@ -8174,37 +8174,37 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>231215</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>530 CO RD 515</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>VERNON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:59 AM</t>
+          <t>08/11/2026 03:37 PM</t>
         </is>
       </c>
       <c r="O106" s="3" t="inlineStr">
@@ -8247,37 +8247,37 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>231215</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>530 CO RD 515</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>VERNON</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:59 AM</t>
+          <t>08/11/2026 03:37 PM</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr">
@@ -8320,37 +8320,37 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>231215</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+          <t>THE BOTTLE SHOP</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>530 CO RD 515</t>
+          <t>366 ESSEX ST</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>VERNON</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:59 AM</t>
+          <t>08/11/2026 03:14 PM</t>
         </is>
       </c>
       <c r="O108" s="3" t="inlineStr">
@@ -8393,37 +8393,37 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>QUICK BUY</t>
+          <t>THE BOTTLE SHOP</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>149 RIDGE RD</t>
+          <t>366 ESSEX ST</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:08 AM</t>
+          <t>08/11/2026 03:14 PM</t>
         </is>
       </c>
       <c r="O109" s="3" t="inlineStr">
@@ -8466,37 +8466,37 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>QUICK BUY</t>
+          <t>THE BOTTLE SHOP</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>149 RIDGE RD</t>
+          <t>366 ESSEX ST</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:08 AM</t>
+          <t>08/11/2026 03:14 PM</t>
         </is>
       </c>
       <c r="O110" s="3" t="inlineStr">
@@ -8539,37 +8539,37 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>QUICK BUY</t>
+          <t>THE BOTTLE SHOP</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>149 RIDGE RD</t>
+          <t>366 ESSEX ST</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:08 AM</t>
+          <t>08/11/2026 03:14 PM</t>
         </is>
       </c>
       <c r="O111" s="3" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Javier Melo</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8627,22 +8627,22 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>QUICK BUY</t>
+          <t>PRESIDENT LIQRS (A)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>149 RIDGE RD</t>
+          <t>158 PRESIDENT ST</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -8666,11 +8666,11 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:08 AM</t>
+          <t>08/11/2026 02:54 PM</t>
         </is>
       </c>
       <c r="O112" s="3" t="inlineStr">
@@ -8685,37 +8685,37 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>47004</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>QUICK BUY</t>
+          <t>WIDES DELI &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>149 RIDGE RD</t>
+          <t>81-85 CENTRAL AVE</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:08 AM</t>
+          <t>08/11/2026 02:30 PM</t>
         </is>
       </c>
       <c r="O113" s="3" t="inlineStr">
@@ -8758,37 +8758,37 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>47004</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>QUICK BUY</t>
+          <t>WIDES DELI &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>149 RIDGE RD</t>
+          <t>81-85 CENTRAL AVE</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:08 AM</t>
+          <t>08/11/2026 02:30 PM</t>
         </is>
       </c>
       <c r="O114" s="3" t="inlineStr">
@@ -8831,37 +8831,37 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>47004</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>PARUTA'S (A)</t>
+          <t>WIDES DELI &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>89 MARKET ST</t>
+          <t>81-85 CENTRAL AVE</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
@@ -8885,11 +8885,11 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 12:52 PM</t>
+          <t>08/11/2026 02:30 PM</t>
         </is>
       </c>
       <c r="O115" s="3" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8914,27 +8914,27 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 10:50 AM</t>
+          <t>08/11/2026 01:00 PM</t>
         </is>
       </c>
       <c r="O116" s="3" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -8987,27 +8987,27 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 10:50 AM</t>
+          <t>08/11/2026 01:00 PM</t>
         </is>
       </c>
       <c r="O117" s="3" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9060,27 +9060,27 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 10:50 AM</t>
+          <t>08/11/2026 01:00 PM</t>
         </is>
       </c>
       <c r="O118" s="3" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9133,27 +9133,27 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 10:50 AM</t>
+          <t>08/11/2026 01:00 PM</t>
         </is>
       </c>
       <c r="O119" s="3" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9206,27 +9206,27 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 10:50 AM</t>
+          <t>08/11/2026 01:00 PM</t>
         </is>
       </c>
       <c r="O120" s="3" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9279,27 +9279,27 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 10:50 AM</t>
+          <t>08/11/2026 01:00 PM</t>
         </is>
       </c>
       <c r="O121" s="3" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9352,27 +9352,27 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>231215</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDO'S (P)</t>
+          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>293 MADISON AVE</t>
+          <t>530 CO RD 515</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>VERNON</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -9396,11 +9396,11 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026 10:29 AM</t>
+          <t>08/11/2026 09:59 AM</t>
         </is>
       </c>
       <c r="O122" s="3" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9425,27 +9425,27 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>25047</t>
+          <t>231215</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>PARKER LIQUORS (Z)</t>
+          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>203 PARKER AVE</t>
+          <t>530 CO RD 515</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>VERNON</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -9469,11 +9469,11 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 04:37 PM</t>
+          <t>08/11/2026 09:59 AM</t>
         </is>
       </c>
       <c r="O123" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9498,27 +9498,27 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>231215</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>BELMONT LIQRS (P)</t>
+          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>146 BELMONT AVENUE</t>
+          <t>530 CO RD 515</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>VERNON</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -9542,11 +9542,11 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 03:46 PM</t>
+          <t>08/11/2026 09:59 AM</t>
         </is>
       </c>
       <c r="O124" s="3" t="inlineStr">
@@ -9561,37 +9561,37 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>231215</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>FARM BOY</t>
+          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>465 GETTY AVE</t>
+          <t>530 CO RD 515</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>VERNON</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -9615,11 +9615,11 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 02:38 PM</t>
+          <t>08/11/2026 09:59 AM</t>
         </is>
       </c>
       <c r="O125" s="3" t="inlineStr">
@@ -9634,68 +9634,1455 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>231215</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>530 CO RD 515</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>VERNON</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>LYTT STRAWBERRY RITA</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>08/11/2026 09:59 AM</t>
+        </is>
+      </c>
+      <c r="O126" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>231215</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>530 CO RD 515</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>VERNON</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>LYTT TROPICAL PUNCH</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>08/11/2026 09:59 AM</t>
+        </is>
+      </c>
+      <c r="O127" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>James Heaney</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>29009</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>QUICK BUY</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>149 RIDGE RD</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>LYNDHURST</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>LYTT BLUE RASPBERRY</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>08/11/2026 09:08 AM</t>
+        </is>
+      </c>
+      <c r="O128" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>James Heaney</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>29009</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>QUICK BUY</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>149 RIDGE RD</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>LYNDHURST</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>LYTT STRAWBERRY RITA</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>08/11/2026 09:08 AM</t>
+        </is>
+      </c>
+      <c r="O129" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>James Heaney</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>29009</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>QUICK BUY</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>149 RIDGE RD</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>LYNDHURST</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>LYTT GRAPE</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>08/11/2026 09:08 AM</t>
+        </is>
+      </c>
+      <c r="O130" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>James Heaney</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>29009</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>QUICK BUY</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>149 RIDGE RD</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>LYNDHURST</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>LYTT LONG ISLAND ICED TEA</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>08/11/2026 09:08 AM</t>
+        </is>
+      </c>
+      <c r="O131" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>James Heaney</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>29009</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>QUICK BUY</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>149 RIDGE RD</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>LYNDHURST</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>LYTT PEACH MANGO</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>08/11/2026 09:08 AM</t>
+        </is>
+      </c>
+      <c r="O132" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>James Heaney</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>29009</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>QUICK BUY</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>149 RIDGE RD</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>LYNDHURST</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>LYTT TROPICAL PUNCH</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>08/11/2026 09:08 AM</t>
+        </is>
+      </c>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>Javier Melo</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>Sales Rep</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Denise Montes</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>20055</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>PARUTA'S (A)</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>89 MARKET ST</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>LYTT LONG ISLAND ICED TEA</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="O134" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>231316</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>PATRICKS WINE BARN</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>38 HAMBURG AVE</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>SUSSEX</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>LYTT BLUE RASPBERRY</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 10:50 AM</t>
+        </is>
+      </c>
+      <c r="O135" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>231316</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>PATRICKS WINE BARN</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>38 HAMBURG AVE</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>SUSSEX</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>LYTT GRAPE</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 10:50 AM</t>
+        </is>
+      </c>
+      <c r="O136" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>231316</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>PATRICKS WINE BARN</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>38 HAMBURG AVE</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>SUSSEX</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>LYTT STRAWBERRY RITA</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 10:50 AM</t>
+        </is>
+      </c>
+      <c r="O137" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>231316</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>PATRICKS WINE BARN</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>38 HAMBURG AVE</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>SUSSEX</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>LYTT LONG ISLAND ICED TEA</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 10:50 AM</t>
+        </is>
+      </c>
+      <c r="O138" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>231316</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>PATRICKS WINE BARN</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>38 HAMBURG AVE</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>SUSSEX</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>LYTT TROPICAL PUNCH</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 10:50 AM</t>
+        </is>
+      </c>
+      <c r="O139" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Jayson Romine</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Paul Deady</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>231316</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>PATRICKS WINE BARN</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>38 HAMBURG AVE</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>SUSSEX</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>LYTT PEACH MANGO</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 10:50 AM</t>
+        </is>
+      </c>
+      <c r="O140" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Javier Melo</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>20069</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDO'S (P)</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>293 MADISON AVE</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>LYTT GRAPE</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>08/07/2026 10:29 AM</t>
+        </is>
+      </c>
+      <c r="O141" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Javier Melo</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>25047</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>PARKER LIQUORS (Z)</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>203 PARKER AVE</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>LYTT LONG ISLAND ICED TEA</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>08/06/2026 04:37 PM</t>
+        </is>
+      </c>
+      <c r="O142" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Javier Melo</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>15059</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>BELMONT LIQRS (P)</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>146 BELMONT AVENUE</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>LYTT STRAWBERRY RITA</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>08/06/2026 03:46 PM</t>
+        </is>
+      </c>
+      <c r="O143" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>patrick infante</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Sales Associate</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>21044</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>FARM BOY</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>465 GETTY AVE</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>PATERSON</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>LYTT</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>LYTT GRAPE</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>08/06/2026 02:38 PM</t>
+        </is>
+      </c>
+      <c r="O144" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Javier Melo</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>21044</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>FARM BOY</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>465 GETTY AVE</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
         <is>
           <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
-      <c r="L126" s="2" t="inlineStr">
-        <is>
-          <t>24 PK</t>
-        </is>
-      </c>
-      <c r="M126" s="2" t="n">
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="N126" s="2" t="inlineStr">
+      <c r="N145" s="2" t="inlineStr">
         <is>
           <t>08/06/2026 01:38 PM</t>
         </is>
       </c>
-      <c r="O126" s="3" t="inlineStr">
+      <c r="O145" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -9828,6 +11215,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9872,7 +11278,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026</t>
+          <t>08/24/2026</t>
         </is>
       </c>
     </row>

--- a/MPOs/off-prem/lytt_pos_displays.xlsx
+++ b/MPOs/off-prem/lytt_pos_displays.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O213"/>
+  <dimension ref="A1:O216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -582,7 +582,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -597,27 +597,27 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>LYTT LLC</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>LYTT AGENT ORANGE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -636,11 +636,11 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 04:33 PM</t>
+          <t>08/26/2026 02:39 PM</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -670,27 +670,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>LYTT LLC</t>
+          <t>BOSTON BEER COMPANY</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>LYTT AGENT ORANGE</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -709,11 +709,11 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 04:20 PM</t>
+          <t>08/26/2026 02:39 PM</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,27 +738,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191010</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR FACTORY II JEFFERSON</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>725 NJ-15</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>LAKE HOPATCONG</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 04:11 PM</t>
+          <t>08/26/2026 02:39 PM</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191010</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR FACTORY II JEFFERSON</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>725 NJ-15</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>LAKE HOPATCONG</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>LYTT LLC</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT AGENT ORANGE</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -855,11 +855,11 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 04:11 PM</t>
+          <t>08/25/2026 04:33 PM</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,32 +884,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>191010</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>LIQUOR FACTORY II JEFFERSON</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>725 NJ-15</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>LAKE HOPATCONG</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>BOSTON BEER COMPANY</t>
+          <t>LYTT LLC</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT AGENT ORANGE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -928,11 +928,11 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 04:11 PM</t>
+          <t>08/25/2026 04:20 PM</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1166,37 +1166,37 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>David Fletcher</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>191010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>HOLLYWD LIQ&amp;DELI (A)</t>
+          <t>LIQUOR FACTORY II JEFFERSON</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40 W PLEASANT AVE</t>
+          <t>725 NJ-15</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>MAYWOOD</t>
+          <t>LAKE HOPATCONG</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4 PK</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 01:46 PM</t>
+          <t>08/25/2026 04:11 PM</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1249,27 +1249,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>191010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>QUICK STOP FOOD &amp; LIQ</t>
+          <t>LIQUOR FACTORY II JEFFERSON</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93 S. MAIN ST</t>
+          <t>725 NJ-15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>LAKE HOPATCONG</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 01:04 PM</t>
+          <t>08/25/2026 04:11 PM</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,27 +1322,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>191010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>QUICK STOP FOOD &amp; LIQ</t>
+          <t>LIQUOR FACTORY II JEFFERSON</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>93 S. MAIN ST</t>
+          <t>725 NJ-15</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>LAKE HOPATCONG</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 01:04 PM</t>
+          <t>08/25/2026 04:11 PM</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>David Fletcher</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1400,22 +1400,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>QUICK STOP FOOD &amp; LIQ</t>
+          <t>HOLLYWD LIQ&amp;DELI (A)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93 S. MAIN ST</t>
+          <t>40 W PLEASANT AVE</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>MAYWOOD</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>4 PK</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 01:04 PM</t>
+          <t>08/25/2026 01:46 PM</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>KRAUSZER LIQUOR</t>
+          <t>QUICK STOP FOOD &amp; LIQ</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>216 MIDLAND AVE</t>
+          <t>93 S. MAIN ST</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 12:48 PM</t>
+          <t>08/25/2026 01:04 PM</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>KRAUSZER LIQUOR</t>
+          <t>QUICK STOP FOOD &amp; LIQ</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>216 MIDLAND AVE</t>
+          <t>93 S. MAIN ST</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 12:48 PM</t>
+          <t>08/25/2026 01:04 PM</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -1619,22 +1619,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>KRAUSZER LIQUOR</t>
+          <t>QUICK STOP FOOD &amp; LIQ</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>216 MIDLAND AVE</t>
+          <t>93 S. MAIN ST</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 12:48 PM</t>
+          <t>08/25/2026 01:04 PM</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>David Fletcher</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1692,22 +1692,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47011</t>
+          <t>76018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD DELI &amp; LIQ</t>
+          <t>KRAUSZER LIQUOR</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>284 TEANECK ROAD</t>
+          <t>216 MIDLAND AVE</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4 PK</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 12:34 PM</t>
+          <t>08/25/2026 12:48 PM</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>David Fletcher</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1765,22 +1765,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47011</t>
+          <t>76018</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD DELI &amp; LIQ</t>
+          <t>KRAUSZER LIQUOR</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>284 TEANECK ROAD</t>
+          <t>216 MIDLAND AVE</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4 PK</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 12:34 PM</t>
+          <t>08/25/2026 12:48 PM</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>David Fletcher</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1838,22 +1838,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47011</t>
+          <t>76018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD DELI &amp; LIQ</t>
+          <t>KRAUSZER LIQUOR</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>284 TEANECK ROAD</t>
+          <t>216 MIDLAND AVE</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4 PK</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 12:34 PM</t>
+          <t>08/25/2026 12:48 PM</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -1911,22 +1911,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>KRAUSZER LIQUOR</t>
+          <t>RIDGEFIELD DELI &amp; LIQ</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>216 MIDLAND AVE</t>
+          <t>284 TEANECK ROAD</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6 PK</t>
+          <t>4 PK</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 12:08 PM</t>
+          <t>08/25/2026 12:34 PM</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>KRAUSZER LIQUOR</t>
+          <t>RIDGEFIELD DELI &amp; LIQ</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>216 MIDLAND AVE</t>
+          <t>284 TEANECK ROAD</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6 PK</t>
+          <t>4 PK</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 12:08 PM</t>
+          <t>08/25/2026 12:34 PM</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -2057,22 +2057,22 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>KRAUSZER LIQUOR</t>
+          <t>RIDGEFIELD DELI &amp; LIQ</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>216 MIDLAND AVE</t>
+          <t>284 TEANECK ROAD</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6 PK</t>
+          <t>4 PK</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 12:08 PM</t>
+          <t>08/25/2026 12:34 PM</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -2130,22 +2130,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76018</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>KRAUSZER LIQUOR</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>216 MIDLAND AVE</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 11:53 AM</t>
+          <t>08/25/2026 12:08 PM</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -2203,22 +2203,22 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>76018</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON DISC LIQ (A)</t>
+          <t>KRAUSZER LIQUOR</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>73 ACKERMAN AVE BOTONY PL</t>
+          <t>216 MIDLAND AVE</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 11:53 AM</t>
+          <t>08/25/2026 12:08 PM</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>David Fletcher</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2276,22 +2276,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>76018</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
+          <t>KRAUSZER LIQUOR</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>206 HACKENSACK ST</t>
+          <t>216 MIDLAND AVE</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>6 PK</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 11:50 AM</t>
+          <t>08/25/2026 12:08 PM</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>David Fletcher</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2349,22 +2349,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
+          <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>206 HACKENSACK ST</t>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>6 PK</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 11:50 AM</t>
+          <t>08/25/2026 11:53 AM</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>David Fletcher</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2422,22 +2422,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
+          <t>CLIFTON DISC LIQ (A)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>206 HACKENSACK ST</t>
+          <t>73 ACKERMAN AVE BOTONY PL</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>WOODRIDGE</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>6 PK</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 11:50 AM</t>
+          <t>08/25/2026 11:53 AM</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -2480,37 +2480,37 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Jay Tabasco</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>230441</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>WINE COUNTRY NEWTON</t>
+          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>49 HAMPTON HOUSE ROAD</t>
+          <t>206 HACKENSACK ST</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>WOODRIDGE</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2525,20 +2525,20 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6 PK</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 11:05 AM</t>
+          <t>08/25/2026 11:50 AM</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>206 HACKENSACK ST</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>WOODRIDGE</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 10:13 AM</t>
+          <t>08/25/2026 11:50 AM</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2641,22 +2641,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>WOODRIDGE WINES &amp; LIQ(A)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>206 HACKENSACK ST</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>WOODRIDGE</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 10:13 AM</t>
+          <t>08/25/2026 11:50 AM</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -2699,37 +2699,37 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Jay Tabasco</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>230441</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>WINE AND FOOD MART (Z)</t>
+          <t>WINE COUNTRY NEWTON</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>589 ANDERSON AVE</t>
+          <t>49 HAMPTON HOUSE ROAD</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>CLIFFSIDE PARK</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2744,20 +2744,20 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>6 PK</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>08/25/2026 10:13 AM</t>
+          <t>08/25/2026 11:05 AM</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3001,27 +3001,27 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC DISCOUNT LIQUORS</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>49 MARKET ST</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3045,11 +3045,11 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 02:12 PM</t>
+          <t>08/25/2026 10:13 AM</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3079,22 +3079,22 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>HOLLYWD LIQ&amp;DELI (A)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>40 W PLEASANT AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>MAYWOOD</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 02:10 PM</t>
+          <t>08/25/2026 10:13 AM</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3152,22 +3152,22 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>HOLLYWD LIQ&amp;DELI (A)</t>
+          <t>WINE AND FOOD MART (Z)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>40 W PLEASANT AVE</t>
+          <t>589 ANDERSON AVE</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>MAYWOOD</t>
+          <t>CLIFFSIDE PARK</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 02:10 PM</t>
+          <t>08/25/2026 10:13 AM</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3220,27 +3220,27 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>HOLLYWD LIQ&amp;DELI (A)</t>
+          <t>PASSAIC DISCOUNT LIQUORS</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>40 W PLEASANT AVE</t>
+          <t>49 MARKET ST</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>MAYWOOD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3264,11 +3264,11 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 02:10 PM</t>
+          <t>08/24/2026 02:12 PM</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3298,22 +3298,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>SHOP-RITE LIQ LYNDHURST</t>
+          <t>HOLLYWD LIQ&amp;DELI (A)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>542 NEW YORK AVE</t>
+          <t>40 W PLEASANT AVE</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>MAYWOOD</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 01:29 PM</t>
+          <t>08/24/2026 02:10 PM</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3371,22 +3371,22 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>SHOP-RITE LIQ LYNDHURST</t>
+          <t>HOLLYWD LIQ&amp;DELI (A)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>542 NEW YORK AVE</t>
+          <t>40 W PLEASANT AVE</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>MAYWOOD</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 01:29 PM</t>
+          <t>08/24/2026 02:10 PM</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3444,22 +3444,22 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>SHOP-RITE LIQ LYNDHURST</t>
+          <t>HOLLYWD LIQ&amp;DELI (A)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>542 NEW YORK AVE</t>
+          <t>40 W PLEASANT AVE</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>MAYWOOD</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 01:29 PM</t>
+          <t>08/24/2026 02:10 PM</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>David Fletcher</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>HOLLYWD LIQ&amp;DELI (A)</t>
+          <t>SHOP-RITE LIQ LYNDHURST</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>40 W PLEASANT AVE</t>
+          <t>542 NEW YORK AVE</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>MAYWOOD</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6 PK</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 01:15 PM</t>
+          <t>08/24/2026 01:29 PM</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>David Fletcher</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3736,22 +3736,22 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>HOLLYWD LIQ&amp;DELI (A)</t>
+          <t>SHOP-RITE LIQ LYNDHURST</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>40 W PLEASANT AVE</t>
+          <t>542 NEW YORK AVE</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>MAYWOOD</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -3766,12 +3766,12 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>6 PK</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 01:15 PM</t>
+          <t>08/24/2026 01:29 PM</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>David Fletcher</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3809,22 +3809,22 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>HOLLYWD LIQ&amp;DELI (A)</t>
+          <t>SHOP-RITE LIQ LYNDHURST</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>40 W PLEASANT AVE</t>
+          <t>542 NEW YORK AVE</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>MAYWOOD</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>6 PK</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 01:15 PM</t>
+          <t>08/24/2026 01:29 PM</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>David Fletcher</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3882,22 +3882,22 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>WIDES DELI &amp; LIQUOR</t>
+          <t>HOLLYWD LIQ&amp;DELI (A)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>81-85 CENTRAL AVE</t>
+          <t>40 W PLEASANT AVE</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>MAYWOOD</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>6 PK</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 01:02 PM</t>
+          <t>08/24/2026 01:15 PM</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>David Fletcher</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3955,22 +3955,22 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>WIDES DELI &amp; LIQUOR</t>
+          <t>HOLLYWD LIQ&amp;DELI (A)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>81-85 CENTRAL AVE</t>
+          <t>40 W PLEASANT AVE</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>MAYWOOD</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>6 PK</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 01:02 PM</t>
+          <t>08/24/2026 01:15 PM</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>David Fletcher</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>WIDES DELI &amp; LIQUOR</t>
+          <t>HOLLYWD LIQ&amp;DELI (A)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>81-85 CENTRAL AVE</t>
+          <t>40 W PLEASANT AVE</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>MAYWOOD</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>6 PK</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 01:02 PM</t>
+          <t>08/24/2026 01:15 PM</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
@@ -4101,17 +4101,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>47004</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>EXQUISITE W &amp; L (A)</t>
+          <t>WIDES DELI &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>215 MAIN ST</t>
+          <t>81-85 CENTRAL AVE</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 12:48 PM</t>
+          <t>08/24/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -4174,17 +4174,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>47004</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>EXQUISITE W &amp; L (A)</t>
+          <t>WIDES DELI &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>215 MAIN ST</t>
+          <t>81-85 CENTRAL AVE</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 12:48 PM</t>
+          <t>08/24/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>47004</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>EXQUISITE W &amp; L (A)</t>
+          <t>WIDES DELI &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>215 MAIN ST</t>
+          <t>81-85 CENTRAL AVE</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 12:48 PM</t>
+          <t>08/24/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 12:47 PM</t>
+          <t>08/24/2026 12:48 PM</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 12:47 PM</t>
+          <t>08/24/2026 12:48 PM</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 12:47 PM</t>
+          <t>08/24/2026 12:48 PM</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>David Fletcher</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4539,22 +4539,22 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>QUICK STOP FOOD &amp; LIQ</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>93 S. MAIN ST</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>12 PK BTL</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 12:44 PM</t>
+          <t>08/24/2026 12:47 PM</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>David Fletcher</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4612,22 +4612,22 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>QUICK STOP FOOD &amp; LIQ</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>93 S. MAIN ST</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>12 PK BTL</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 12:44 PM</t>
+          <t>08/24/2026 12:47 PM</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
@@ -4685,22 +4685,22 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>EXQUISITE W &amp; L (A)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>215 MAIN ST</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 11:37 AM</t>
+          <t>08/24/2026 12:47 PM</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>David Fletcher</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4758,22 +4758,22 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>QUICK STOP FOOD &amp; LIQ</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>93 S. MAIN ST</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>12 PK BTL</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 11:37 AM</t>
+          <t>08/24/2026 12:44 PM</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>David Fletcher</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4831,22 +4831,22 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>QUICK STOP FOOD &amp; LIQ</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>93 S. MAIN ST</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>12 PK BTL</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 11:37 AM</t>
+          <t>08/24/2026 12:44 PM</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -5108,37 +5108,37 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>36006</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON LIQUOR AND WINE</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>168 MAIN AVE</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 10:11 AM</t>
+          <t>08/24/2026 11:37 AM</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
@@ -5181,37 +5181,37 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>36006</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON LIQUOR AND WINE</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>168 MAIN AVE</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 10:11 AM</t>
+          <t>08/24/2026 11:37 AM</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
@@ -5254,37 +5254,37 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>36006</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON LIQUOR AND WINE</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>168 MAIN AVE</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>08/24/2026 10:11 AM</t>
+          <t>08/24/2026 11:37 AM</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -5561,22 +5561,22 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>36006</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>CAPRI DELI&amp;LIQ (P)</t>
+          <t>WALLINGTON LIQUOR AND WINE</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>226 PATERSON AVE</t>
+          <t>168 MAIN AVE</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026 12:25 PM</t>
+          <t>08/24/2026 10:11 AM</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
@@ -5634,22 +5634,22 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>36006</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>CAPRI DELI&amp;LIQ (P)</t>
+          <t>WALLINGTON LIQUOR AND WINE</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>226 PATERSON AVE</t>
+          <t>168 MAIN AVE</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026 12:25 PM</t>
+          <t>08/24/2026 10:11 AM</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
@@ -5707,22 +5707,22 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>36006</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>CAPRI DELI&amp;LIQ (P)</t>
+          <t>WALLINGTON LIQUOR AND WINE</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>226 PATERSON AVE</t>
+          <t>168 MAIN AVE</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026 12:25 PM</t>
+          <t>08/24/2026 10:11 AM</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -5999,17 +5999,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026 12:03 PM</t>
+          <t>08/21/2026 12:25 PM</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
@@ -6072,17 +6072,17 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026 12:03 PM</t>
+          <t>08/21/2026 12:25 PM</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
@@ -6145,17 +6145,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>576 PATERSON AVE</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026 12:03 PM</t>
+          <t>08/21/2026 12:25 PM</t>
         </is>
       </c>
       <c r="O78" s="3" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6437,22 +6437,22 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>EAST SIDE BAR LIQUORS</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>442 10TH AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -6476,11 +6476,11 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026 11:26 AM</t>
+          <t>08/21/2026 12:03 PM</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
@@ -6510,22 +6510,22 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>36007</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE OF WALLINGTON</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>375 PATERSON AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026 11:20 AM</t>
+          <t>08/21/2026 12:03 PM</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
@@ -6583,22 +6583,22 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>36007</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE OF WALLINGTON</t>
+          <t>METRO LIQUORS (EAST RUTHERFORD)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>375 PATERSON AVE</t>
+          <t>576 PATERSON AVE</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026 11:20 AM</t>
+          <t>08/21/2026 12:03 PM</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Javier Melo</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6656,22 +6656,22 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>36007</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE OF WALLINGTON</t>
+          <t>EAST SIDE BAR LIQUORS</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>375 PATERSON AVE</t>
+          <t>442 10TH AVE</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -6695,11 +6695,11 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>08/21/2026 11:20 AM</t>
+          <t>08/21/2026 11:26 AM</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -6948,17 +6948,17 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>SHOP RITE OF WALLINGTON</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>375 PATERSON AVE</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 01:19 PM</t>
+          <t>08/21/2026 11:20 AM</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
@@ -7021,17 +7021,17 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>SHOP RITE OF WALLINGTON</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>375 PATERSON AVE</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 01:19 PM</t>
+          <t>08/21/2026 11:20 AM</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
@@ -7094,17 +7094,17 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>SHOP RITE OF WALLINGTON</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>375 PATERSON AVE</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 01:19 PM</t>
+          <t>08/21/2026 11:20 AM</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -7386,22 +7386,22 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 12:51 PM</t>
+          <t>08/20/2026 01:19 PM</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
@@ -7459,22 +7459,22 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 12:51 PM</t>
+          <t>08/20/2026 01:19 PM</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
@@ -7532,22 +7532,22 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>08/20/2026 12:51 PM</t>
+          <t>08/20/2026 01:19 PM</t>
         </is>
       </c>
       <c r="O97" s="3" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Pablo Lopez</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7824,22 +7824,22 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -7863,11 +7863,11 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>08/19/2026 01:26 PM</t>
+          <t>08/20/2026 12:51 PM</t>
         </is>
       </c>
       <c r="O101" s="3" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>phil Ernst</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7892,27 +7892,27 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -7936,11 +7936,11 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 03:19 PM</t>
+          <t>08/20/2026 12:51 PM</t>
         </is>
       </c>
       <c r="O102" s="3" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -7970,22 +7970,22 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>REGALADO LIQ</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>168 MARKET ST</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:41 PM</t>
+          <t>08/20/2026 12:51 PM</t>
         </is>
       </c>
       <c r="O103" s="3" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Pablo Lopez</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -8082,11 +8082,11 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:41 PM</t>
+          <t>08/19/2026 01:26 PM</t>
         </is>
       </c>
       <c r="O104" s="3" t="inlineStr">
@@ -8101,37 +8101,37 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>phil Ernst</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -8155,11 +8155,11 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:05 PM</t>
+          <t>08/18/2026 03:19 PM</t>
         </is>
       </c>
       <c r="O105" s="3" t="inlineStr">
@@ -8189,22 +8189,22 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:05 PM</t>
+          <t>08/18/2026 01:41 PM</t>
         </is>
       </c>
       <c r="O106" s="3" t="inlineStr">
@@ -8262,22 +8262,22 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>WHOOPEE LIQ (A)</t>
+          <t>REGALADO LIQ</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>194 VAN WINKLE AVE</t>
+          <t>168 MARKET ST</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>GARFIELD</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 01:05 PM</t>
+          <t>08/18/2026 01:41 PM</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
@@ -8408,22 +8408,22 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 12:32 PM</t>
+          <t>08/18/2026 01:05 PM</t>
         </is>
       </c>
       <c r="O109" s="3" t="inlineStr">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 12:32 PM</t>
+          <t>08/18/2026 01:05 PM</t>
         </is>
       </c>
       <c r="O110" s="3" t="inlineStr">
@@ -8554,22 +8554,22 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>36016</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>KING LIQUORS</t>
+          <t>WHOOPEE LIQ (A)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>434 MAIN AVE</t>
+          <t>194 VAN WINKLE AVE</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>WALLINGTON</t>
+          <t>GARFIELD</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 12:32 PM</t>
+          <t>08/18/2026 01:05 PM</t>
         </is>
       </c>
       <c r="O111" s="3" t="inlineStr">
@@ -8612,12 +8612,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8627,22 +8627,22 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>C TOWN SUPERMARKET(P)</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>444 20TH AVENUE</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -8666,11 +8666,11 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:24 AM</t>
+          <t>08/18/2026 12:32 PM</t>
         </is>
       </c>
       <c r="O112" s="3" t="inlineStr">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -8700,22 +8700,22 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>WORLD OF WINE &amp; LIQUOR</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>419 VALLEY BROOK AVE.</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:04 AM</t>
+          <t>08/18/2026 12:32 PM</t>
         </is>
       </c>
       <c r="O113" s="3" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -8773,22 +8773,22 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>WORLD OF WINE &amp; LIQUOR</t>
+          <t>KING LIQUORS</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>419 VALLEY BROOK AVE.</t>
+          <t>434 MAIN AVE</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>WALLINGTON</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:04 AM</t>
+          <t>08/18/2026 12:32 PM</t>
         </is>
       </c>
       <c r="O114" s="3" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Javier Melo</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8846,22 +8846,22 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>29011</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>WORLD OF WINE &amp; LIQUOR</t>
+          <t>C TOWN SUPERMARKET(P)</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>419 VALLEY BROOK AVE.</t>
+          <t>444 20TH AVENUE</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
@@ -8885,11 +8885,11 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 11:04 AM</t>
+          <t>08/18/2026 11:24 AM</t>
         </is>
       </c>
       <c r="O115" s="3" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -9138,22 +9138,22 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>CAPRI DELI&amp;LIQ (P)</t>
+          <t>WORLD OF WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>226 PATERSON AVE</t>
+          <t>419 VALLEY BROOK AVE.</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 10:30 AM</t>
+          <t>08/18/2026 11:04 AM</t>
         </is>
       </c>
       <c r="O119" s="3" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -9211,22 +9211,22 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>CAPRI DELI&amp;LIQ (P)</t>
+          <t>WORLD OF WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>226 PATERSON AVE</t>
+          <t>419 VALLEY BROOK AVE.</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 10:30 AM</t>
+          <t>08/18/2026 11:04 AM</t>
         </is>
       </c>
       <c r="O120" s="3" t="inlineStr">
@@ -9269,12 +9269,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -9284,22 +9284,22 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>CAPRI DELI&amp;LIQ (P)</t>
+          <t>WORLD OF WINE &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>226 PATERSON AVE</t>
+          <t>419 VALLEY BROOK AVE.</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>EAST RUTHERFORD</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 10:30 AM</t>
+          <t>08/18/2026 11:04 AM</t>
         </is>
       </c>
       <c r="O121" s="3" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Jay Tabasco</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9425,27 +9425,27 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>190304</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>SHOPPERS DISC LIQUOR</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>65-69 N BEVERWYCK RD</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>LAKE HIAWATHA</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -9460,20 +9460,20 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>12 PK BTL</t>
+          <t>24 PK</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>08/18/2026 09:41 AM</t>
+          <t>08/18/2026 10:30 AM</t>
         </is>
       </c>
       <c r="O123" s="3" t="inlineStr">
@@ -9488,37 +9488,37 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -9542,11 +9542,11 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 01:26 PM</t>
+          <t>08/18/2026 10:30 AM</t>
         </is>
       </c>
       <c r="O124" s="3" t="inlineStr">
@@ -9561,37 +9561,37 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>patrick infante</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>CAPRI DELI&amp;LIQ (P)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>226 PATERSON AVE</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -9615,11 +9615,11 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 01:26 PM</t>
+          <t>08/18/2026 10:30 AM</t>
         </is>
       </c>
       <c r="O125" s="3" t="inlineStr">
@@ -9634,37 +9634,37 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>Jay Tabasco</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>190304</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>SHOPPERS DISC LIQUOR</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>65-69 N BEVERWYCK RD</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>LAKE HIAWATHA</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -9679,20 +9679,20 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>24 PK</t>
+          <t>12 PK BTL</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 01:26 PM</t>
+          <t>08/18/2026 09:41 AM</t>
         </is>
       </c>
       <c r="O126" s="3" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
@@ -9868,22 +9868,22 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
@@ -9907,11 +9907,11 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 12:11 PM</t>
+          <t>08/17/2026 01:26 PM</t>
         </is>
       </c>
       <c r="O129" s="3" t="inlineStr">
@@ -9941,22 +9941,22 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
@@ -9980,11 +9980,11 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 12:11 PM</t>
+          <t>08/17/2026 01:26 PM</t>
         </is>
       </c>
       <c r="O130" s="3" t="inlineStr">
@@ -10014,22 +10014,22 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>WINE AND LIQ DEPOT(A)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>310 HUYLER ST</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>SOUTH HACKENSAC</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
@@ -10053,11 +10053,11 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:23 AM</t>
+          <t>08/17/2026 01:26 PM</t>
         </is>
       </c>
       <c r="O131" s="3" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10082,27 +10082,27 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW LIQUOR (P)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>292 LAKEVIEW AVE</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -10126,11 +10126,11 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:00 AM</t>
+          <t>08/17/2026 12:11 PM</t>
         </is>
       </c>
       <c r="O132" s="3" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10155,27 +10155,27 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW LIQUOR (P)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>292 LAKEVIEW AVE</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -10199,11 +10199,11 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:00 AM</t>
+          <t>08/17/2026 12:11 PM</t>
         </is>
       </c>
       <c r="O133" s="3" t="inlineStr">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>RAINBOW LIQUOR (P)</t>
+          <t>WINE AND LIQ DEPOT(A)</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>292 LAKEVIEW AVE</t>
+          <t>310 HUYLER ST</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SOUTH HACKENSAC</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 10:00 AM</t>
+          <t>08/17/2026 10:23 AM</t>
         </is>
       </c>
       <c r="O134" s="3" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10520,27 +10520,27 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>RAINBOW LIQUOR (P)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>292 LAKEVIEW AVE</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -10564,11 +10564,11 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>08/14/2026 12:06 PM</t>
+          <t>08/17/2026 10:00 AM</t>
         </is>
       </c>
       <c r="O138" s="3" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10593,27 +10593,27 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>RAINBOW LIQUOR (P)</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>292 LAKEVIEW AVE</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
@@ -10637,11 +10637,11 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>08/14/2026 11:41 AM</t>
+          <t>08/17/2026 10:00 AM</t>
         </is>
       </c>
       <c r="O139" s="3" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Dave Ehlers</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10666,27 +10666,27 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
+          <t>RAINBOW LIQUOR (P)</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>1001 MAIN ST</t>
+          <t>292 LAKEVIEW AVE</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>RIVER EDGE</t>
+          <t>CLIFTON</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>08/14/2026 11:39 AM</t>
+          <t>08/17/2026 10:00 AM</t>
         </is>
       </c>
       <c r="O140" s="3" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>08/14/2026 11:38 AM</t>
+          <t>08/14/2026 12:06 PM</t>
         </is>
       </c>
       <c r="O141" s="3" t="inlineStr">
@@ -10802,37 +10802,37 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Gallagher</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Christopher McCrohan</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>BEST CELLARS (WANAQUE)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>1069 RINGWOOD AVE</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>WANAQUE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -10856,11 +10856,11 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:38 PM</t>
+          <t>08/14/2026 11:41 AM</t>
         </is>
       </c>
       <c r="O142" s="3" t="inlineStr">
@@ -10875,37 +10875,37 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Gallagher</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Christopher McCrohan</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>BEST CELLARS (WANAQUE)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>1069 RINGWOOD AVE</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>WANAQUE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:38 PM</t>
+          <t>08/14/2026 11:39 AM</t>
         </is>
       </c>
       <c r="O143" s="3" t="inlineStr">
@@ -10948,37 +10948,37 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Vaughn Gallagher</t>
+          <t>Dave Ehlers</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Christopher McCrohan</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>BEST CELLARS (WANAQUE)</t>
+          <t>TOTAL WINE &amp; MORE (RIVER EDGE)</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>1069 RINGWOOD AVE</t>
+          <t>1001 MAIN ST</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>WANAQUE</t>
+          <t>RIVER EDGE</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -11002,11 +11002,11 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:38 PM</t>
+          <t>08/14/2026 11:38 AM</t>
         </is>
       </c>
       <c r="O144" s="3" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L147" s="2" t="inlineStr">
@@ -11240,37 +11240,37 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Vaughn Gallagher</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Christopher McCrohan</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>BEST CELLARS (WANAQUE)</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>1069 RINGWOOD AVE</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WANAQUE</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:02 PM</t>
+          <t>08/13/2026 01:38 PM</t>
         </is>
       </c>
       <c r="O148" s="3" t="inlineStr">
@@ -11313,37 +11313,37 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Vaughn Gallagher</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Christopher McCrohan</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>BEST CELLARS (WANAQUE)</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>1069 RINGWOOD AVE</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WANAQUE</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:02 PM</t>
+          <t>08/13/2026 01:38 PM</t>
         </is>
       </c>
       <c r="O149" s="3" t="inlineStr">
@@ -11386,37 +11386,37 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Chris Payton</t>
+          <t>Vaughn Gallagher</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Christopher McCrohan</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
+          <t>BEST CELLARS (WANAQUE)</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>66 MARKET ST</t>
+          <t>1069 RINGWOOD AVE</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>SADDLE BROOK</t>
+          <t>WANAQUE</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 01:02 PM</t>
+          <t>08/13/2026 01:38 PM</t>
         </is>
       </c>
       <c r="O150" s="3" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L153" s="2" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11693,22 +11693,22 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>LINWOOD WINE-LINWOOD PLAZA</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>102 LINWOOD PLAZA</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>FORT LEE</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 11:05 AM</t>
+          <t>08/13/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O154" s="3" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11766,22 +11766,22 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>LINWOOD WINE-LINWOOD PLAZA</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>102 LINWOOD PLAZA</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>FORT LEE</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L155" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 11:05 AM</t>
+          <t>08/13/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O155" s="3" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Daniel La Gala</t>
+          <t>Chris Payton</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11839,22 +11839,22 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>LINWOOD WINE-LINWOOD PLAZA</t>
+          <t>USA WINE TRADERS CLUB (SADDLE BROOK)</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>102 LINWOOD PLAZA</t>
+          <t>66 MARKET ST</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>FORT LEE</t>
+          <t>SADDLE BROOK</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 11:05 AM</t>
+          <t>08/13/2026 01:02 PM</t>
         </is>
       </c>
       <c r="O156" s="3" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12126,27 +12126,27 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>49027</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>LINWOOD WINE-LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>102 LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>FORT LEE</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 10:51 AM</t>
+          <t>08/13/2026 11:05 AM</t>
         </is>
       </c>
       <c r="O160" s="3" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12199,27 +12199,27 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>49027</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>LINWOOD WINE-LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>102 LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>FORT LEE</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L161" s="2" t="inlineStr">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 10:51 AM</t>
+          <t>08/13/2026 11:05 AM</t>
         </is>
       </c>
       <c r="O161" s="3" t="inlineStr">
@@ -12262,7 +12262,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Matthew Powierski</t>
+          <t>Daniel La Gala</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12272,27 +12272,27 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>49027</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>WINE GRAND (CARLSTADT)</t>
+          <t>LINWOOD WINE-LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>675 PATERSON AVE</t>
+          <t>102 LINWOOD PLAZA</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>CARLSTADT</t>
+          <t>FORT LEE</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>08/13/2026 10:51 AM</t>
+          <t>08/13/2026 11:05 AM</t>
         </is>
       </c>
       <c r="O162" s="3" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L163" s="2" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
@@ -12554,37 +12554,37 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 04:00 PM</t>
+          <t>08/13/2026 10:51 AM</t>
         </is>
       </c>
       <c r="O166" s="3" t="inlineStr">
@@ -12627,37 +12627,37 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L167" s="2" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 04:00 PM</t>
+          <t>08/13/2026 10:51 AM</t>
         </is>
       </c>
       <c r="O167" s="3" t="inlineStr">
@@ -12700,37 +12700,37 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Matthew Powierski</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>83001</t>
+          <t>32017</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>FOOD UNIVERSE MARKETPLACE</t>
+          <t>WINE GRAND (CARLSTADT)</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>937 LINCOLN AVE</t>
+          <t>675 PATERSON AVE</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>GLEN ROCK</t>
+          <t>CARLSTADT</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 04:00 PM</t>
+          <t>08/13/2026 10:51 AM</t>
         </is>
       </c>
       <c r="O168" s="3" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L169" s="2" t="inlineStr">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
@@ -12934,22 +12934,22 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:37 PM</t>
+          <t>08/11/2026 04:00 PM</t>
         </is>
       </c>
       <c r="O171" s="3" t="inlineStr">
@@ -13007,22 +13007,22 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:37 PM</t>
+          <t>08/11/2026 04:00 PM</t>
         </is>
       </c>
       <c r="O172" s="3" t="inlineStr">
@@ -13080,22 +13080,22 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>83001</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>SHOP RITE LIQ (PARAMUS)</t>
+          <t>FOOD UNIVERSE MARKETPLACE</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>224 RT 4 E</t>
+          <t>937 LINCOLN AVE</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>PARAMUS</t>
+          <t>GLEN ROCK</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:37 PM</t>
+          <t>08/11/2026 04:00 PM</t>
         </is>
       </c>
       <c r="O173" s="3" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L175" s="2" t="inlineStr">
@@ -13299,22 +13299,22 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>THE BOTTLE SHOP</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>366 ESSEX ST</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:14 PM</t>
+          <t>08/11/2026 03:37 PM</t>
         </is>
       </c>
       <c r="O176" s="3" t="inlineStr">
@@ -13372,22 +13372,22 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>THE BOTTLE SHOP</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>366 ESSEX ST</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L177" s="2" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:14 PM</t>
+          <t>08/11/2026 03:37 PM</t>
         </is>
       </c>
       <c r="O177" s="3" t="inlineStr">
@@ -13445,22 +13445,22 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>THE BOTTLE SHOP</t>
+          <t>SHOP RITE LIQ (PARAMUS)</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>366 ESSEX ST</t>
+          <t>224 RT 4 E</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>PARAMUS</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 03:14 PM</t>
+          <t>08/11/2026 03:37 PM</t>
         </is>
       </c>
       <c r="O178" s="3" t="inlineStr">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L179" s="2" t="inlineStr">
@@ -13576,37 +13576,37 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>27002</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>PRESIDENT LIQRS (A)</t>
+          <t>THE BOTTLE SHOP</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>158 PRESIDENT ST</t>
+          <t>366 ESSEX ST</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>PASSAIC</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
@@ -13630,11 +13630,11 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 02:54 PM</t>
+          <t>08/11/2026 03:14 PM</t>
         </is>
       </c>
       <c r="O180" s="3" t="inlineStr">
@@ -13664,22 +13664,22 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>WIDES DELI &amp; LIQUOR</t>
+          <t>THE BOTTLE SHOP</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>81-85 CENTRAL AVE</t>
+          <t>366 ESSEX ST</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L181" s="2" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="N181" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 02:30 PM</t>
+          <t>08/11/2026 03:14 PM</t>
         </is>
       </c>
       <c r="O181" s="3" t="inlineStr">
@@ -13737,22 +13737,22 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>WIDES DELI &amp; LIQUOR</t>
+          <t>THE BOTTLE SHOP</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>81-85 CENTRAL AVE</t>
+          <t>366 ESSEX ST</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="N182" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 02:30 PM</t>
+          <t>08/11/2026 03:14 PM</t>
         </is>
       </c>
       <c r="O182" s="3" t="inlineStr">
@@ -13795,37 +13795,37 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Nicholas Micco</t>
+          <t>Javier Melo</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Michael Engel</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>WIDES DELI &amp; LIQUOR</t>
+          <t>PRESIDENT LIQRS (A)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>81-85 CENTRAL AVE</t>
+          <t>158 PRESIDENT ST</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>RIDGEFIELD PARK</t>
+          <t>PASSAIC</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L183" s="2" t="inlineStr">
@@ -13849,11 +13849,11 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N183" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 02:30 PM</t>
+          <t>08/11/2026 02:54 PM</t>
         </is>
       </c>
       <c r="O183" s="3" t="inlineStr">
@@ -13868,37 +13868,37 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>47004</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>WIDES DELI &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>81-85 CENTRAL AVE</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="N184" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 01:00 PM</t>
+          <t>08/11/2026 02:30 PM</t>
         </is>
       </c>
       <c r="O184" s="3" t="inlineStr">
@@ -13941,37 +13941,37 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>47004</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>WIDES DELI &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>81-85 CENTRAL AVE</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="N185" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 01:00 PM</t>
+          <t>08/11/2026 02:30 PM</t>
         </is>
       </c>
       <c r="O185" s="3" t="inlineStr">
@@ -14014,37 +14014,37 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Nicholas Micco</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Sales Rep</t>
+          <t>Sales Associate</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Michael Engel</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>47004</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>LUCKY 7 (A)</t>
+          <t>WIDES DELI &amp; LIQUOR</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>77 RIVER RD</t>
+          <t>81-85 CENTRAL AVE</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>NORTH ARLINGTON</t>
+          <t>RIDGEFIELD PARK</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="N186" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 01:00 PM</t>
+          <t>08/11/2026 02:30 PM</t>
         </is>
       </c>
       <c r="O186" s="3" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L187" s="2" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -14316,27 +14316,27 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>231215</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>530 CO RD 515</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>VERNON</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="N190" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:59 AM</t>
+          <t>08/11/2026 01:00 PM</t>
         </is>
       </c>
       <c r="O190" s="3" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -14389,27 +14389,27 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>231215</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>530 CO RD 515</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>VERNON</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L191" s="2" t="inlineStr">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="N191" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:59 AM</t>
+          <t>08/11/2026 01:00 PM</t>
         </is>
       </c>
       <c r="O191" s="3" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -14462,27 +14462,27 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>231215</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
+          <t>LUCKY 7 (A)</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>530 CO RD 515</t>
+          <t>77 RIVER RD</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>VERNON</t>
+          <t>NORTH ARLINGTON</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="N192" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:59 AM</t>
+          <t>08/11/2026 01:00 PM</t>
         </is>
       </c>
       <c r="O192" s="3" t="inlineStr">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L195" s="2" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -14754,27 +14754,27 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>231215</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>QUICK BUY</t>
+          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>149 RIDGE RD</t>
+          <t>530 CO RD 515</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>VERNON</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:08 AM</t>
+          <t>08/11/2026 09:59 AM</t>
         </is>
       </c>
       <c r="O196" s="3" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -14827,27 +14827,27 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>231215</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>QUICK BUY</t>
+          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>149 RIDGE RD</t>
+          <t>530 CO RD 515</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>VERNON</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="N197" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:08 AM</t>
+          <t>08/11/2026 09:59 AM</t>
         </is>
       </c>
       <c r="O197" s="3" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>James Heaney</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -14900,27 +14900,27 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>231215</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>QUICK BUY</t>
+          <t>MAC &amp; LINDY'S W &amp; S (A)</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>149 RIDGE RD</t>
+          <t>530 CO RD 515</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>LYNDHURST</t>
+          <t>VERNON</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="N198" s="2" t="inlineStr">
         <is>
-          <t>08/11/2026 09:08 AM</t>
+          <t>08/11/2026 09:59 AM</t>
         </is>
       </c>
       <c r="O198" s="3" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L199" s="2" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L201" s="2" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -15197,22 +15197,22 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>PARUTA'S (A)</t>
+          <t>QUICK BUY</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>89 MARKET ST</t>
+          <t>149 RIDGE RD</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
@@ -15236,11 +15236,11 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 12:52 PM</t>
+          <t>08/11/2026 09:08 AM</t>
         </is>
       </c>
       <c r="O202" s="3" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -15265,27 +15265,27 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>QUICK BUY</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>149 RIDGE RD</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
@@ -15300,7 +15300,7 @@
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
-          <t>LYTT BLUE RASPBERRY</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L203" s="2" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="N203" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 10:50 AM</t>
+          <t>08/11/2026 09:08 AM</t>
         </is>
       </c>
       <c r="O203" s="3" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>James Heaney</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -15338,27 +15338,27 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>QUICK BUY</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>149 RIDGE RD</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>LYNDHURST</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L204" s="2" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 10:50 AM</t>
+          <t>08/11/2026 09:08 AM</t>
         </is>
       </c>
       <c r="O204" s="3" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Jayson Romine</t>
+          <t>Javier Melo</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -15411,27 +15411,27 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Paul Deady</t>
+          <t>Denise Montes</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>231316</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>PATRICKS WINE BARN</t>
+          <t>PARUTA'S (A)</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>38 HAMBURG AVE</t>
+          <t>89 MARKET ST</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>SUSSEX</t>
+          <t>PATERSON</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L205" s="2" t="inlineStr">
@@ -15455,11 +15455,11 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>08/10/2026 10:50 AM</t>
+          <t>08/10/2026 12:52 PM</t>
         </is>
       </c>
       <c r="O205" s="3" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT BLUE RASPBERRY</t>
         </is>
       </c>
       <c r="L206" s="2" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
-          <t>LYTT TROPICAL PUNCH</t>
+          <t>LYTT GRAPE</t>
         </is>
       </c>
       <c r="L207" s="2" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>LYTT PEACH MANGO</t>
+          <t>LYTT STRAWBERRY RITA</t>
         </is>
       </c>
       <c r="L208" s="2" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -15703,27 +15703,27 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDO'S (P)</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>293 MADISON AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
-          <t>LYTT GRAPE</t>
+          <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
       <c r="L209" s="2" t="inlineStr">
@@ -15747,11 +15747,11 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026 10:29 AM</t>
+          <t>08/10/2026 10:50 AM</t>
         </is>
       </c>
       <c r="O209" s="3" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -15776,27 +15776,27 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>25047</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>PARKER LIQUORS (Z)</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>203 PARKER AVE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>CLIFTON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>LYTT LONG ISLAND ICED TEA</t>
+          <t>LYTT TROPICAL PUNCH</t>
         </is>
       </c>
       <c r="L210" s="2" t="inlineStr">
@@ -15820,11 +15820,11 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N210" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 04:37 PM</t>
+          <t>08/10/2026 10:50 AM</t>
         </is>
       </c>
       <c r="O210" s="3" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Javier Melo</t>
+          <t>Jayson Romine</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -15849,27 +15849,27 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Denise Montes</t>
+          <t>Paul Deady</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>231316</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>BELMONT LIQRS (P)</t>
+          <t>PATRICKS WINE BARN</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>146 BELMONT AVENUE</t>
+          <t>38 HAMBURG AVE</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>PATERSON</t>
+          <t>SUSSEX</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>LYTT STRAWBERRY RITA</t>
+          <t>LYTT PEACH MANGO</t>
         </is>
       </c>
       <c r="L211" s="2" t="inlineStr">
@@ -15893,11 +15893,11 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N211" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 03:46 PM</t>
+          <t>08/10/2026 10:50 AM</t>
         </is>
       </c>
       <c r="O211" s="3" t="inlineStr">
@@ -15912,12 +15912,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>patrick infante</t>
+          <t>Javier Melo</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Sales Associate</t>
+          <t>Sales Rep</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -15927,17 +15927,17 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>FARM BOY</t>
+          <t>SEGUNDO'S (P)</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>465 GETTY AVE</t>
+          <t>293 MADISON AVE</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -15966,11 +15966,11 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 02:38 PM</t>
+          <t>08/07/2026 10:29 AM</t>
         </is>
       </c>
       <c r="O212" s="3" t="inlineStr">
@@ -16000,53 +16000,272 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
+          <t>25047</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>PARKER LIQUORS (Z)</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>203 PARKER AVE</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>CLIFTON</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>LYTT LONG ISLAND ICED TEA</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>08/06/2026 04:37 PM</t>
+        </is>
+      </c>
+      <c r="O213" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Javier Melo</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>15059</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>BELMONT LIQRS (P)</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>146 BELMONT AVENUE</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>LYTT STRAWBERRY RITA</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>08/06/2026 03:46 PM</t>
+        </is>
+      </c>
+      <c r="O214" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>patrick infante</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Sales Associate</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
           <t>21044</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>FARM BOY</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr">
         <is>
           <t>465 GETTY AVE</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>PATERSON</t>
         </is>
       </c>
-      <c r="I213" s="2" t="inlineStr">
-        <is>
-          <t>BOSTON BEER COMPANY</t>
-        </is>
-      </c>
-      <c r="J213" s="2" t="inlineStr">
-        <is>
-          <t>LYTT</t>
-        </is>
-      </c>
-      <c r="K213" s="2" t="inlineStr">
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>LYTT GRAPE</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>08/06/2026 02:38 PM</t>
+        </is>
+      </c>
+      <c r="O215" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Javier Melo</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Denise Montes</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>21044</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>FARM BOY</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>465 GETTY AVE</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>PATERSON</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>BOSTON BEER COMPANY</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>LYTT</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr">
         <is>
           <t>LYTT LONG ISLAND ICED TEA</t>
         </is>
       </c>
-      <c r="L213" s="2" t="inlineStr">
-        <is>
-          <t>24 PK</t>
-        </is>
-      </c>
-      <c r="M213" s="2" t="n">
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>24 PK</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="N213" s="2" t="inlineStr">
+      <c r="N216" s="2" t="inlineStr">
         <is>
           <t>08/06/2026 01:38 PM</t>
         </is>
       </c>
-      <c r="O213" s="3" t="inlineStr">
+      <c r="O216" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -16266,6 +16485,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId211"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId215"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16310,7 +16532,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>08/26/2026</t>
+          <t>08/27/2026</t>
         </is>
       </c>
     </row>
